--- a/product_selector_out/STM32C0 series.xlsx
+++ b/product_selector_out/STM32C0 series.xlsx
@@ -37002,7 +37002,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 23. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37024,7 +37024,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 23. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37046,7 +37046,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 23. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37068,7 +37068,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37090,7 +37090,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37112,7 +37112,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37134,7 +37134,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37156,7 +37156,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37178,7 +37178,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37200,7 +37200,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37222,7 +37222,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37244,7 +37244,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37266,7 +37266,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37288,7 +37288,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37310,7 +37310,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37332,7 +37332,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37354,7 +37354,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37376,7 +37376,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37398,7 +37398,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37420,7 +37420,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37442,7 +37442,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37464,7 +37464,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37486,7 +37486,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37508,7 +37508,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37530,7 +37530,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37552,7 +37552,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37574,7 +37574,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37596,7 +37596,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37618,7 +37618,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37640,7 +37640,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37662,7 +37662,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37684,7 +37684,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37706,7 +37706,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37728,7 +37728,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37750,7 +37750,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37772,7 +37772,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37794,7 +37794,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37816,7 +37816,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 23. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37838,7 +37838,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 23. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37860,7 +37860,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37882,7 +37882,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37904,7 +37904,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37926,7 +37926,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37948,7 +37948,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37970,7 +37970,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -37992,7 +37992,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -38014,7 +38014,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -38036,7 +38036,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -38058,7 +38058,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -38080,7 +38080,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -38102,7 +38102,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -38124,7 +38124,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -38146,7 +38146,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -38168,7 +38168,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32C0 series.xlsx
+++ b/product_selector_out/STM32C0 series.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM65"/>
+  <dimension ref="A1:BN65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7265625" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c011d6.pdf</t>
         </is>
       </c>
@@ -1641,6 +1653,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c011d6.pdf</t>
         </is>
       </c>
@@ -1968,6 +1985,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c011d6.pdf</t>
         </is>
       </c>
@@ -2295,6 +2317,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c031c4.pdf</t>
         </is>
       </c>
@@ -2622,6 +2649,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c031c4.pdf</t>
         </is>
       </c>
@@ -2949,6 +2981,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c031c4.pdf</t>
         </is>
       </c>
@@ -3276,6 +3313,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c031c4.pdf</t>
         </is>
       </c>
@@ -3603,6 +3645,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c031c4.pdf</t>
         </is>
       </c>
@@ -3930,6 +3977,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c051c6.pdf</t>
         </is>
       </c>
@@ -4257,6 +4309,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c051c6.pdf</t>
         </is>
       </c>
@@ -4584,6 +4641,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c031c4.pdf</t>
         </is>
       </c>
@@ -4911,6 +4973,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c031c4.pdf</t>
         </is>
       </c>
@@ -5238,6 +5305,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c031c4.pdf</t>
         </is>
       </c>
@@ -5565,6 +5637,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c091kb.pdf</t>
         </is>
       </c>
@@ -5892,6 +5969,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c091kb.pdf</t>
         </is>
       </c>
@@ -6219,6 +6301,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c091kb.pdf</t>
         </is>
       </c>
@@ -6546,6 +6633,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c091kb.pdf</t>
         </is>
       </c>
@@ -6873,6 +6965,11 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c091kb.pdf</t>
         </is>
       </c>
@@ -7200,6 +7297,11 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c091kb.pdf</t>
         </is>
       </c>
@@ -7527,6 +7629,11 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c091kb.pdf</t>
         </is>
       </c>
@@ -7854,6 +7961,11 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c091kb.pdf</t>
         </is>
       </c>
@@ -8181,6 +8293,11 @@
       </c>
       <c r="BM33" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c091kb.pdf</t>
         </is>
       </c>
@@ -8508,6 +8625,11 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c091kb.pdf</t>
         </is>
       </c>
@@ -8835,6 +8957,11 @@
       </c>
       <c r="BM35" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c091kb.pdf</t>
         </is>
       </c>
@@ -9162,6 +9289,11 @@
       </c>
       <c r="BM36" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN36" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c051c6.pdf</t>
         </is>
       </c>
@@ -9489,6 +9621,11 @@
       </c>
       <c r="BM37" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN37" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c071r8.pdf</t>
         </is>
       </c>
@@ -9816,6 +9953,11 @@
       </c>
       <c r="BM38" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN38" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c051c6.pdf</t>
         </is>
       </c>
@@ -10143,6 +10285,11 @@
       </c>
       <c r="BM39" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN39" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c091kb.pdf</t>
         </is>
       </c>
@@ -10470,6 +10617,11 @@
       </c>
       <c r="BM40" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN40" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c071r8.pdf</t>
         </is>
       </c>
@@ -10797,6 +10949,11 @@
       </c>
       <c r="BM41" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN41" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c051c6.pdf</t>
         </is>
       </c>
@@ -11124,6 +11281,11 @@
       </c>
       <c r="BM42" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN42" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c071r8.pdf</t>
         </is>
       </c>
@@ -11451,6 +11613,11 @@
       </c>
       <c r="BM43" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN43" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c051c6.pdf</t>
         </is>
       </c>
@@ -11778,6 +11945,11 @@
       </c>
       <c r="BM44" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN44" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c051c6.pdf</t>
         </is>
       </c>
@@ -12105,6 +12277,11 @@
       </c>
       <c r="BM45" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN45" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c091kb.pdf</t>
         </is>
       </c>
@@ -12432,6 +12609,11 @@
       </c>
       <c r="BM46" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN46" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c051c6.pdf</t>
         </is>
       </c>
@@ -12759,6 +12941,11 @@
       </c>
       <c r="BM47" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN47" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c051c6.pdf</t>
         </is>
       </c>
@@ -13086,6 +13273,11 @@
       </c>
       <c r="BM48" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN48" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c091kb.pdf</t>
         </is>
       </c>
@@ -13413,6 +13605,11 @@
       </c>
       <c r="BM49" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN49" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c011d6.pdf</t>
         </is>
       </c>
@@ -13740,6 +13937,11 @@
       </c>
       <c r="BM50" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN50" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c011d6.pdf</t>
         </is>
       </c>
@@ -14067,6 +14269,11 @@
       </c>
       <c r="BM51" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN51" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c091kb.pdf</t>
         </is>
       </c>
@@ -14394,6 +14601,11 @@
       </c>
       <c r="BM52" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN52" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c091kb.pdf</t>
         </is>
       </c>
@@ -14721,6 +14933,11 @@
       </c>
       <c r="BM53" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN53" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c091kb.pdf</t>
         </is>
       </c>
@@ -15048,6 +15265,11 @@
       </c>
       <c r="BM54" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN54" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c071r8.pdf</t>
         </is>
       </c>
@@ -15375,6 +15597,11 @@
       </c>
       <c r="BM55" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN55" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c071r8.pdf</t>
         </is>
       </c>
@@ -15702,6 +15929,11 @@
       </c>
       <c r="BM56" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN56" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c091kb.pdf</t>
         </is>
       </c>
@@ -16029,6 +16261,11 @@
       </c>
       <c r="BM57" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN57" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c091kb.pdf</t>
         </is>
       </c>
@@ -16356,6 +16593,11 @@
       </c>
       <c r="BM58" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN58" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c091kb.pdf</t>
         </is>
       </c>
@@ -16683,6 +16925,11 @@
       </c>
       <c r="BM59" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN59" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c091kb.pdf</t>
         </is>
       </c>
@@ -17010,6 +17257,11 @@
       </c>
       <c r="BM60" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN60" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c091kb.pdf</t>
         </is>
       </c>
@@ -17337,6 +17589,11 @@
       </c>
       <c r="BM61" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN61" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c071r8.pdf</t>
         </is>
       </c>
@@ -17664,6 +17921,11 @@
       </c>
       <c r="BM62" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN62" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c071r8.pdf</t>
         </is>
       </c>
@@ -17991,6 +18253,11 @@
       </c>
       <c r="BM63" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN63" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c071r8.pdf</t>
         </is>
       </c>
@@ -18318,6 +18585,11 @@
       </c>
       <c r="BM64" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN64" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c071r8.pdf</t>
         </is>
       </c>
@@ -18645,12 +18917,17 @@
       </c>
       <c r="BM65" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN65" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c071r8.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -18671,16 +18948,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -18693,6 +18968,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -18712,7 +18988,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -18783,7 +19061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM65"/>
+  <dimension ref="A1:BN65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -18851,6 +19129,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19184,6 +19463,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -19279,6 +19563,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -19601,7 +19886,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19928,7 +20218,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20255,7 +20550,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20582,7 +20882,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20909,7 +21214,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21236,7 +21546,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21563,7 +21878,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21890,7 +22210,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -22217,7 +22542,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -22544,7 +22874,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -22871,7 +23206,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -23198,7 +23538,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -23525,7 +23870,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -23852,7 +24202,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -24179,7 +24534,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -24506,7 +24866,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -24833,7 +25198,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -25160,7 +25530,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -25487,7 +25862,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
+      <c r="BM30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -25814,7 +26194,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
+      <c r="BM31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -26141,7 +26526,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
+      <c r="BM32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -26468,7 +26858,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM33" s="6" t="inlineStr">
+      <c r="BM33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -26795,7 +27190,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM34" s="6" t="inlineStr">
+      <c r="BM34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -27122,7 +27522,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM35" s="6" t="inlineStr">
+      <c r="BM35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -27449,7 +27854,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM36" s="6" t="inlineStr">
+      <c r="BM36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN36" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -27776,7 +28186,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM37" s="6" t="inlineStr">
+      <c r="BM37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN37" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -28103,7 +28518,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM38" s="6" t="inlineStr">
+      <c r="BM38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN38" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -28430,7 +28850,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM39" s="6" t="inlineStr">
+      <c r="BM39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN39" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -28757,7 +29182,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM40" s="6" t="inlineStr">
+      <c r="BM40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN40" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -29084,7 +29514,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM41" s="6" t="inlineStr">
+      <c r="BM41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN41" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -29411,7 +29846,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM42" s="6" t="inlineStr">
+      <c r="BM42" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN42" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -29738,7 +30178,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM43" s="6" t="inlineStr">
+      <c r="BM43" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN43" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30065,7 +30510,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM44" s="6" t="inlineStr">
+      <c r="BM44" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN44" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30392,7 +30842,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM45" s="6" t="inlineStr">
+      <c r="BM45" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN45" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30719,7 +31174,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM46" s="6" t="inlineStr">
+      <c r="BM46" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN46" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31046,7 +31506,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM47" s="6" t="inlineStr">
+      <c r="BM47" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN47" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31373,7 +31838,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM48" s="6" t="inlineStr">
+      <c r="BM48" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN48" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31700,7 +32170,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM49" s="6" t="inlineStr">
+      <c r="BM49" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN49" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32027,7 +32502,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM50" s="6" t="inlineStr">
+      <c r="BM50" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN50" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32354,7 +32834,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM51" s="6" t="inlineStr">
+      <c r="BM51" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN51" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32681,7 +33166,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM52" s="6" t="inlineStr">
+      <c r="BM52" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN52" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33008,7 +33498,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM53" s="6" t="inlineStr">
+      <c r="BM53" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN53" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33335,7 +33830,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM54" s="6" t="inlineStr">
+      <c r="BM54" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN54" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33662,7 +34162,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM55" s="6" t="inlineStr">
+      <c r="BM55" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN55" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33989,7 +34494,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM56" s="6" t="inlineStr">
+      <c r="BM56" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN56" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34316,7 +34826,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM57" s="6" t="inlineStr">
+      <c r="BM57" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN57" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34643,7 +35158,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM58" s="6" t="inlineStr">
+      <c r="BM58" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN58" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34970,7 +35490,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM59" s="6" t="inlineStr">
+      <c r="BM59" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN59" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35297,7 +35822,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM60" s="6" t="inlineStr">
+      <c r="BM60" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN60" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35624,7 +36154,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM61" s="6" t="inlineStr">
+      <c r="BM61" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN61" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35951,7 +36486,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM62" s="6" t="inlineStr">
+      <c r="BM62" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN62" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36278,7 +36818,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM63" s="6" t="inlineStr">
+      <c r="BM63" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN63" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36605,7 +37150,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM64" s="6" t="inlineStr">
+      <c r="BM64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN64" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36932,7 +37482,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM65" s="6" t="inlineStr">
+      <c r="BM65" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN65" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36940,8 +37495,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
